--- a/data/industry/TrendForce/Li-Ion Battery.xlsx
+++ b/data/industry/TrendForce/Li-Ion Battery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82F6B4F6-543A-420F-B496-B2A6A8042D02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786FBC09-CCA0-46F8-89FD-72A788B3E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Battery Cell &amp; Pack" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,9 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
@@ -267,23 +270,23 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -296,7 +299,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -333,7 +336,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -343,40 +346,40 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -655,17 +658,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -705,7 +708,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>46028</v>
       </c>
@@ -750,7 +753,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>46064</v>
       </c>
@@ -795,7 +798,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46090</v>
       </c>
@@ -840,17 +843,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93A7413-903B-41E3-BDE3-CD88FC030C93}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -896,7 +899,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>46028</v>
       </c>
@@ -947,7 +950,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>46064</v>
       </c>
@@ -998,7 +1001,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46090</v>
       </c>
@@ -1051,17 +1054,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0866DC8-FCF3-4C5E-83C2-1F3B814AC134}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1103,7 +1106,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>46028</v>
       </c>
@@ -1150,7 +1153,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>46064</v>
       </c>
@@ -1197,7 +1200,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46090</v>
       </c>
@@ -1244,17 +1247,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE236D12-0519-456D-89C0-C829EF6FE190}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1290,7 +1293,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>46028</v>
       </c>
@@ -1331,7 +1334,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>46064</v>
       </c>
@@ -1372,7 +1375,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46090</v>
       </c>
@@ -1410,17 +1413,17 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B864B0A-C2A5-4EA0-8D10-4C40685755EC}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +1457,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>46028</v>
       </c>
@@ -1493,7 +1496,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>46064</v>
       </c>
@@ -1532,7 +1535,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46090</v>
       </c>
@@ -1567,18 +1570,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64F3CCF-5660-444E-BF2D-168013FA393D}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.7265625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1620,7 +1623,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>46028</v>
       </c>
@@ -1667,7 +1670,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>46064</v>
       </c>
@@ -1714,7 +1717,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46090</v>
       </c>
@@ -1761,18 +1764,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9B3F37-91A5-425D-8E2F-CBD919F64D9B}">
   <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.08984375" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.36328125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.36328125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
+    <row r="1" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1802,7 +1805,7 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="14">
         <v>46028</v>
       </c>
@@ -1837,7 +1840,7 @@
       <c r="T2" s="3"/>
       <c r="U2" s="3"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" s="14">
         <v>46064</v>
       </c>
@@ -1872,7 +1875,7 @@
       <c r="T3" s="3"/>
       <c r="U3" s="3"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="14">
         <v>46090</v>
       </c>
@@ -1901,19 +1904,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940B0638-7F42-42A0-B176-F348356A0E0B}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.6328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B1" s="10" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
         <v>60</v>
       </c>
@@ -1924,43 +1927,43 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="10"/>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="10"/>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="10"/>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="10"/>
       <c r="B7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
       <c r="B8" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="10" t="s">
         <v>61</v>
       </c>
@@ -1968,61 +1971,61 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="10"/>
       <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="10"/>
       <c r="B11" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="10"/>
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="10"/>
       <c r="B13" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="10"/>
       <c r="B14" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="10"/>
       <c r="B15" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="10"/>
       <c r="B16" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="10"/>
       <c r="B17" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="10"/>
       <c r="B18" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
         <v>62</v>
       </c>
@@ -2030,49 +2033,49 @@
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A20" s="10"/>
       <c r="B20" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="10"/>
       <c r="B21" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A22" s="10"/>
       <c r="B22" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A23" s="10"/>
       <c r="B23" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A25" s="10"/>
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A26" s="10"/>
       <c r="B26" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A27" s="10" t="s">
         <v>63</v>
       </c>
@@ -2080,31 +2083,31 @@
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A28" s="10"/>
       <c r="B28" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A30" s="10"/>
       <c r="B30" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A31" s="10"/>
       <c r="B31" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A32" s="10" t="s">
         <v>64</v>
       </c>
@@ -2112,25 +2115,25 @@
         <v>45</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A33" s="10"/>
       <c r="B33" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A34" s="10"/>
       <c r="B34" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A35" s="10"/>
       <c r="B35" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A36" s="10" t="s">
         <v>65</v>
       </c>
@@ -2138,49 +2141,49 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A37" s="10"/>
       <c r="B37" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A38" s="10"/>
       <c r="B38" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A39" s="10"/>
       <c r="B39" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A40" s="10"/>
       <c r="B40" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A41" s="10"/>
       <c r="B41" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A42" s="10"/>
       <c r="B42" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A43" s="10"/>
       <c r="B43" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A44" s="10" t="s">
         <v>66</v>
       </c>
@@ -2188,7 +2191,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A45" s="10"/>
       <c r="B45" s="1" t="s">
         <v>58</v>

--- a/data/industry/TrendForce/Li-Ion Battery.xlsx
+++ b/data/industry/TrendForce/Li-Ion Battery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm12\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786FBC09-CCA0-46F8-89FD-72A788B3E414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB88D8B8-7ACB-4AF6-9CFA-3ACE3B35B29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5790" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Battery Cell &amp; Pack" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="68">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -657,13 +654,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
@@ -833,6 +830,41 @@
         <v>0.49</v>
       </c>
     </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.38</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.59</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.35</v>
+      </c>
+      <c r="I5" s="7">
+        <v>8.25</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.72</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -842,13 +874,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93A7413-903B-41E3-BDE3-CD88FC030C93}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
@@ -1043,6 +1075,50 @@
       </c>
       <c r="N4" s="7">
         <v>5.29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1.2</v>
+      </c>
+      <c r="F5" s="7">
+        <v>10.59</v>
+      </c>
+      <c r="G5" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="H5" s="7">
+        <v>11.73</v>
+      </c>
+      <c r="I5" s="7">
+        <v>18.29</v>
+      </c>
+      <c r="J5" s="7">
+        <v>18.53</v>
+      </c>
+      <c r="K5" s="7">
+        <v>20.399999999999999</v>
+      </c>
+      <c r="L5" s="7">
+        <v>5.55</v>
+      </c>
+      <c r="M5" s="7">
+        <v>39.76</v>
+      </c>
+      <c r="N5" s="7">
+        <v>5.54</v>
       </c>
     </row>
   </sheetData>
@@ -1053,13 +1129,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0866DC8-FCF3-4C5E-83C2-1F3B814AC134}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
@@ -1238,6 +1314,44 @@
         <v>5.2</v>
       </c>
     </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.75</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.9</v>
+      </c>
+      <c r="G5" s="7">
+        <v>2.12</v>
+      </c>
+      <c r="H5" s="7">
+        <v>2.67</v>
+      </c>
+      <c r="I5" s="7">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="J5" s="7">
+        <v>2.13</v>
+      </c>
+      <c r="K5" s="7">
+        <v>2.95</v>
+      </c>
+      <c r="L5" s="7">
+        <v>5.2</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1246,13 +1360,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE236D12-0519-456D-89C0-C829EF6FE190}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
@@ -1404,6 +1518,35 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>0.45</v>
+      </c>
+      <c r="F5" s="7">
+        <v>0.85</v>
+      </c>
+      <c r="G5" s="7">
+        <v>0.83</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="I5" s="7">
+        <v>1.1299999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1412,13 +1555,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B864B0A-C2A5-4EA0-8D10-4C40685755EC}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
   </cols>
@@ -1561,6 +1704,32 @@
         <v>4.9000000000000004</v>
       </c>
     </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>11.21</v>
+      </c>
+      <c r="F5" s="7">
+        <v>3.17</v>
+      </c>
+      <c r="G5" s="7">
+        <v>3.1</v>
+      </c>
+      <c r="H5" s="7">
+        <v>4.7</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1569,13 +1738,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F64F3CCF-5660-444E-BF2D-168013FA393D}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.69921875" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
@@ -1755,6 +1924,44 @@
         <v>3.24</v>
       </c>
     </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="12">
+        <v>2221</v>
+      </c>
+      <c r="F5" s="7">
+        <v>15.67</v>
+      </c>
+      <c r="G5" s="7">
+        <v>15.29</v>
+      </c>
+      <c r="H5" s="7">
+        <v>42.91</v>
+      </c>
+      <c r="I5" s="7">
+        <v>37.07</v>
+      </c>
+      <c r="J5" s="7">
+        <v>9.59</v>
+      </c>
+      <c r="K5" s="7">
+        <v>13.94</v>
+      </c>
+      <c r="L5" s="7">
+        <v>3.21</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1763,13 +1970,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC9B3F37-91A5-425D-8E2F-CBD919F64D9B}">
-  <dimension ref="A1:U4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.09765625" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.3984375" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.59765625" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.5" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="21" width="9" style="7"/>
     <col min="22" max="16384" width="9" style="4"/>
@@ -1895,6 +2102,26 @@
         <v>1.45</v>
       </c>
     </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="B5" s="14">
+        <v>46125</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="7">
+        <v>1.95</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1.5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1904,9 +2131,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{940B0638-7F42-42A0-B176-F348356A0E0B}">
   <dimension ref="A1:C45"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="32.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.59765625" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68" style="4" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="4"/>
   </cols>

--- a/data/industry/TrendForce/Li-Ion Battery.xlsx
+++ b/data/industry/TrendForce/Li-Ion Battery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1333199D-6AAC-4141-8688-567A2DA4C175}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1579F13-6501-4370-A3A8-E704A297C1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11430" yWindow="0" windowWidth="11700" windowHeight="14730" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Battery Cell &amp; Pack" sheetId="1" r:id="rId1"/>
@@ -272,7 +272,7 @@
     <numFmt numFmtId="166" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -313,6 +313,14 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -337,7 +345,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -373,6 +381,33 @@
     <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -655,283 +690,283 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.453125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="21" width="9" style="7"/>
-    <col min="22" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="10.08984375" style="20" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="22" bestFit="1" customWidth="1"/>
+    <col min="5" max="21" width="9" style="25"/>
+    <col min="22" max="16384" width="9" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:21" s="19" customFormat="1">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="2" spans="1:21">
-      <c r="A2" s="14">
+      <c r="A2" s="20">
         <v>46028</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="20">
         <v>46028</v>
       </c>
-      <c r="C2" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="C2" s="21">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D2" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="23">
         <v>0.49</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="23">
         <v>0.35</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="23">
         <v>0.52</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="23">
         <v>0.33</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="23">
         <v>7.63</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="23">
         <v>0.65</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="23">
         <v>0.46</v>
       </c>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="3"/>
-      <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
+      <c r="L2" s="23"/>
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="23"/>
     </row>
     <row r="3" spans="1:21">
-      <c r="A3" s="14">
+      <c r="A3" s="20">
         <v>46064</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="20">
         <v>46064</v>
       </c>
-      <c r="C3" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="C3" s="21">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="23">
         <v>0.52</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="23">
         <v>0.36</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="23">
         <v>0.55000000000000004</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3" s="23">
         <v>0.34</v>
       </c>
-      <c r="I3" s="3">
+      <c r="I3" s="23">
         <v>7.84</v>
       </c>
-      <c r="J3" s="3">
+      <c r="J3" s="23">
         <v>0.67</v>
       </c>
-      <c r="K3" s="3">
+      <c r="K3" s="23">
         <v>0.48</v>
       </c>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
-      <c r="S3" s="3"/>
-      <c r="T3" s="3"/>
-      <c r="U3" s="3"/>
+      <c r="L3" s="23"/>
+      <c r="M3" s="23"/>
+      <c r="N3" s="23"/>
+      <c r="O3" s="23"/>
+      <c r="P3" s="23"/>
+      <c r="Q3" s="23"/>
+      <c r="R3" s="23"/>
+      <c r="S3" s="23"/>
+      <c r="T3" s="23"/>
+      <c r="U3" s="23"/>
     </row>
     <row r="4" spans="1:21">
-      <c r="A4" s="14">
+      <c r="A4" s="20">
         <v>46090</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="20">
         <v>46090</v>
       </c>
-      <c r="C4" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="C4" s="21">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="25">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="25">
         <v>0.37</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="25">
         <v>0.57999999999999996</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="25">
         <v>0.35</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="25">
         <v>8.2100000000000009</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="25">
         <v>0.7</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="25">
         <v>0.49</v>
       </c>
     </row>
     <row r="5" spans="1:21">
-      <c r="A5" s="14">
+      <c r="A5" s="20">
         <v>46125</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="20">
         <v>46125</v>
       </c>
-      <c r="C5" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="7">
+      <c r="C5" s="21">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="25">
         <v>0.57999999999999996</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="25">
         <v>0.38</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="25">
         <v>0.59</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="25">
         <v>0.35</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="25">
         <v>8.25</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="25">
         <v>0.72</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="25">
         <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:21">
-      <c r="A6" s="14">
+      <c r="A6" s="20">
         <v>46157</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="20">
         <v>46157</v>
       </c>
-      <c r="C6" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="7">
+      <c r="C6" s="21">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="25">
         <v>0.59</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="25">
         <v>0.38</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="25">
         <v>0.6</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="25">
         <v>0.36</v>
       </c>
-      <c r="I6" s="7">
+      <c r="I6" s="25">
         <v>8.25</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="25">
         <v>0.74</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="25">
         <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:21">
-      <c r="A7" s="14">
+      <c r="A7" s="20">
         <v>46178</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="20">
         <v>46178</v>
       </c>
-      <c r="C7" s="5">
-        <v>0.75694444444444453</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="7">
+      <c r="C7" s="21">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="25">
         <v>0.6</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="25">
         <v>0.39</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="25">
         <v>0.61</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="25">
         <v>0.37</v>
       </c>
-      <c r="I7" s="7">
+      <c r="I7" s="25">
         <v>8.32</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="25">
         <v>0.76</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="25">
         <v>0.51</v>
       </c>
     </row>
